--- a/static/templates/true-up_template.xlsx
+++ b/static/templates/true-up_template.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkb00\PROJECTS\GitRepos\mkb0020-Vercel\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC7DC49-68AD-4DEC-8274-2F59EE5FA91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D223C15-3C33-4DFD-A4B2-77B5B2600010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A5EC922C-524D-4274-B1B7-4F37FFE75EC6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A5EC922C-524D-4274-B1B7-4F37FFE75EC6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="5" r:id="rId1"/>
-    <sheet name="SIGMA-001" sheetId="4" r:id="rId2"/>
+    <sheet name="Summary" sheetId="6" r:id="rId1"/>
+    <sheet name="SIGMA-001" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
   <si>
     <t>SKU</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Remaining Duration (Months)</t>
   </si>
   <si>
-    <t>Subscription ID</t>
-  </si>
-  <si>
     <t>Report Date</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>Procurement Plan</t>
   </si>
   <si>
-    <t>Sigma ID</t>
-  </si>
-  <si>
     <t>Next True Delta Date</t>
   </si>
   <si>
@@ -156,9 +150,6 @@
     <t>PSI Account</t>
   </si>
   <si>
-    <t>**** THIS IS NOT AN ACTUAL REPORT AND IT DOES NOT CONTAIN REAL CUSTOMER OR RESELLER INFORMATION ****</t>
-  </si>
-  <si>
     <t xml:space="preserve">ZephyrusWave    </t>
   </si>
   <si>
@@ -300,20 +291,23 @@
     <t>Adjustment</t>
   </si>
   <si>
-    <t>Usage Category</t>
-  </si>
-  <si>
     <t>YES</t>
   </si>
   <si>
     <t>NO</t>
+  </si>
+  <si>
+    <t>License Shift Eligible</t>
+  </si>
+  <si>
+    <t>Agreement ID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,12 +332,6 @@
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -426,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -434,23 +422,23 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -465,17 +453,17 @@
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -485,12 +473,16 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -838,8 +830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78D4AEE-EE29-40AB-8D87-06ED6D1FE2AE}">
-  <sheetPr codeName="Sheet3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7367F9CF-732D-4061-8C06-464750F2A73C}">
   <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -853,10 +844,10 @@
   <sheetData>
     <row r="1" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -885,10 +876,10 @@
     </row>
     <row r="2" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -917,10 +908,10 @@
     </row>
     <row r="3" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -949,10 +940,10 @@
     </row>
     <row r="4" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -981,10 +972,10 @@
     </row>
     <row r="5" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="12">
-        <v>45741</v>
+        <v>46106</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1013,10 +1004,10 @@
     </row>
     <row r="6" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="12">
-        <v>46836</v>
+        <v>47201</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -1045,7 +1036,7 @@
     </row>
     <row r="7" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="12">
         <v>46023</v>
@@ -1077,10 +1068,10 @@
     </row>
     <row r="8" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="12">
-        <v>46106</v>
+        <v>46471</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -1109,7 +1100,7 @@
     </row>
     <row r="9" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3">
         <v>36</v>
@@ -1141,7 +1132,7 @@
     </row>
     <row r="10" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10" s="3">
         <v>24</v>
@@ -1173,9 +1164,11 @@
     </row>
     <row r="11" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="B11" s="2">
+        <v>245052</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1259,13 +1252,13 @@
     </row>
     <row r="14" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="16" t="s">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>5</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>6</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="10"/>
@@ -1293,15 +1286,13 @@
     </row>
     <row r="15" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B15" s="13">
-        <f>B5</f>
-        <v>45741</v>
+        <v>46106</v>
       </c>
       <c r="C15" s="13">
-        <f>B6</f>
-        <v>46836</v>
+        <v>47201</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="10"/>
@@ -1357,7 +1348,7 @@
     </row>
     <row r="17" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -1385,13 +1376,13 @@
     </row>
     <row r="18" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="10"/>
       <c r="I18" s="1"/>
@@ -1415,10 +1406,14 @@
     </row>
     <row r="19" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="B19" s="14">
+        <v>107.58267607582677</v>
+      </c>
+      <c r="C19" s="2">
+        <v>21043.199999999997</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1441,10 +1436,14 @@
     </row>
     <row r="20" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="19"/>
+        <v>39</v>
+      </c>
+      <c r="B20" s="14">
+        <v>108.9291439563963</v>
+      </c>
+      <c r="C20" s="19">
+        <v>13368</v>
+      </c>
       <c r="D20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1467,17 +1466,25 @@
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="19"/>
+        <v>46</v>
+      </c>
+      <c r="B21" s="14">
+        <v>112.29289999602688</v>
+      </c>
+      <c r="C21" s="19">
+        <v>22276.80000000001</v>
+      </c>
     </row>
     <row r="22" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="19"/>
+        <v>53</v>
+      </c>
+      <c r="B22" s="14">
+        <v>157.62693197253938</v>
+      </c>
+      <c r="C22" s="19">
+        <v>188364</v>
+      </c>
       <c r="D22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1548,9 +1555,7 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="21" x14ac:dyDescent="0.5">
-      <c r="A25" s="15" t="s">
-        <v>39</v>
-      </c>
+      <c r="A25" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1558,8 +1563,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D44DF24-B602-4DC5-876C-D1716B2F6767}">
-  <sheetPr codeName="Sheet4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB5301D-C394-47E3-B78C-4F20DE6AF8AC}">
   <dimension ref="A1:V24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1570,7 +1574,7 @@
     <col min="5" max="5" width="14.08984375" customWidth="1"/>
     <col min="6" max="6" width="12.26953125" customWidth="1"/>
     <col min="7" max="7" width="13.1796875" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" customWidth="1"/>
+    <col min="8" max="8" width="11.36328125" style="25" customWidth="1"/>
     <col min="9" max="9" width="13.6328125" customWidth="1"/>
     <col min="10" max="10" width="14.36328125" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
@@ -1589,84 +1593,83 @@
   <sheetData>
     <row r="1" spans="1:22" s="23" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="I1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="J1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="O1" s="17" t="s">
         <v>16</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="N1" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="O1" s="17" t="s">
-        <v>17</v>
       </c>
       <c r="P1" s="17" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R1" s="17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T1" s="17" t="s">
         <v>2</v>
       </c>
       <c r="U1" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V1" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="D2" s="3">
-        <f>F2-E2</f>
         <v>0</v>
       </c>
       <c r="E2" s="6">
@@ -1675,33 +1678,28 @@
       <c r="F2" s="6">
         <v>100</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="8">
+        <v>21043.199999999997</v>
+      </c>
       <c r="I2" s="7">
-        <f t="shared" ref="I2:I7" si="0">O2*E2*T2</f>
         <v>72000</v>
       </c>
       <c r="J2" s="7">
-        <f t="shared" ref="J2:J7" si="1">F2*O2*T2</f>
         <v>72000</v>
       </c>
       <c r="K2" s="7">
-        <f t="shared" ref="K2:K7" si="2">IF(D2&gt;0, 0, (-1)*D2*O2*T2)</f>
         <v>0</v>
       </c>
       <c r="L2" s="7">
-        <f t="shared" ref="L2:L7" si="3">IF(U2="FIXED", 0, IF(D2&lt;0, 0, D2*O2*T2))</f>
         <v>0</v>
       </c>
       <c r="M2" s="3">
-        <f>IF(U2 = "YES", IF(D2&gt;=0, 0, ((-1)*D2)), 0)</f>
         <v>0</v>
       </c>
       <c r="N2" s="3">
-        <f>IF(U2 = "YES", IF(D2&lt;0, 0, D2), 0)</f>
         <v>0</v>
       </c>
       <c r="O2" s="8">
-        <f>Q2-(Q2*(P2/100))</f>
         <v>30</v>
       </c>
       <c r="P2" s="3">
@@ -1710,37 +1708,33 @@
       <c r="Q2" s="18">
         <v>75</v>
       </c>
-      <c r="R2" s="9" t="str">
-        <f t="shared" ref="R2:R7" si="4">IF(E2&gt;F2, "YES", "NO")</f>
-        <v>NO</v>
+      <c r="R2" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S2" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T2" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="V2" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3">
-        <f>F3-E3</f>
         <v>-1</v>
       </c>
       <c r="E3" s="6">
@@ -1749,33 +1743,26 @@
       <c r="F3" s="6">
         <v>9</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="8"/>
       <c r="I3" s="7">
-        <f>O3*E3*T3</f>
         <v>68352</v>
       </c>
       <c r="J3" s="7">
-        <f>F3*O3*T3</f>
         <v>61516.800000000003</v>
       </c>
       <c r="K3" s="7">
-        <f>IF(D3&gt;0, 0, (-1)*D3*O3*T3)</f>
         <v>6835.2000000000007</v>
       </c>
       <c r="L3" s="7">
-        <f>IF(U3="FIXED", 0, IF(D3&lt;0, 0, D3*O3*T3))</f>
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <f t="shared" ref="M3:M24" si="5">IF(U3 = "YES", IF(D3&gt;=0, 0, ((-1)*D3)), 0)</f>
         <v>1</v>
       </c>
       <c r="N3" s="3">
-        <f t="shared" ref="N3:N24" si="6">IF(U3 = "YES", IF(D3&lt;0, 0, D3), 0)</f>
         <v>0</v>
       </c>
       <c r="O3" s="8">
-        <f>Q3-(Q3*(P3/100))</f>
         <v>284.8</v>
       </c>
       <c r="P3" s="3">
@@ -1784,37 +1771,33 @@
       <c r="Q3" s="18">
         <v>712</v>
       </c>
-      <c r="R3" s="9" t="str">
-        <f>IF(E3&gt;F3, "YES", "NO")</f>
-        <v>YES</v>
+      <c r="R3" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="S3" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T3" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="V3" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="D4" s="3">
-        <f>F4-E4</f>
         <v>200</v>
       </c>
       <c r="E4" s="3">
@@ -1824,33 +1807,26 @@
         <v>200</v>
       </c>
       <c r="G4" s="9"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="8"/>
       <c r="I4" s="7">
-        <f>O4*E4*T4</f>
         <v>0</v>
       </c>
       <c r="J4" s="7">
-        <f>F4*O4*T4</f>
         <v>122880</v>
       </c>
       <c r="K4" s="7">
-        <f>IF(D4&gt;0, 0, (-1)*D4*O4*T4)</f>
         <v>0</v>
       </c>
       <c r="L4" s="7">
-        <f>IF(U4="FIXED", 0, IF(D4&lt;0, 0, D4*O4*T4))</f>
         <v>122880</v>
       </c>
       <c r="M4" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N4" s="3">
-        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="O4" s="8">
-        <f>Q4-(Q4*(P4/100))</f>
         <v>25.6</v>
       </c>
       <c r="P4" s="3">
@@ -1859,37 +1835,33 @@
       <c r="Q4" s="18">
         <v>64</v>
       </c>
-      <c r="R4" s="9" t="str">
-        <f>IF(E4&gt;F4, "YES", "NO")</f>
-        <v>NO</v>
+      <c r="R4" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S4" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T4" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D5" s="22">
-        <f t="shared" ref="D5" si="7">F5-E5</f>
         <v>-15</v>
       </c>
       <c r="E5" s="3">
@@ -1899,33 +1871,26 @@
         <v>0</v>
       </c>
       <c r="G5" s="9"/>
-      <c r="H5" s="7"/>
+      <c r="H5" s="8"/>
       <c r="I5" s="7">
-        <f t="shared" ref="I5" si="8">O5*E5*T5</f>
         <v>135360</v>
       </c>
       <c r="J5" s="7">
-        <f t="shared" ref="J5" si="9">F5*O5*T5</f>
         <v>0</v>
       </c>
       <c r="K5" s="7">
-        <f t="shared" ref="K5" si="10">IF(D5&gt;0, 0, (-1)*D5*O5*T5)</f>
         <v>135360</v>
       </c>
       <c r="L5" s="7">
-        <f t="shared" ref="L5" si="11">IF(U5="FIXED", 0, IF(D5&lt;0, 0, D5*O5*T5))</f>
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="N5" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O5" s="8">
-        <f t="shared" ref="O5" si="12">Q5-(Q5*(P5/100))</f>
         <v>376</v>
       </c>
       <c r="P5" s="3">
@@ -1934,37 +1899,33 @@
       <c r="Q5" s="18">
         <v>940</v>
       </c>
-      <c r="R5" s="9" t="str">
-        <f t="shared" ref="R5" si="13">IF(E5&gt;F5, "YES", "NO")</f>
-        <v>YES</v>
+      <c r="R5" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="S5" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T5" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="V5" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="D6" s="3">
-        <f t="shared" ref="D6" si="14">F6-E6</f>
         <v>0</v>
       </c>
       <c r="E6" s="3">
@@ -1974,33 +1935,26 @@
         <v>5</v>
       </c>
       <c r="G6" s="9"/>
-      <c r="H6" s="3"/>
+      <c r="H6" s="8"/>
       <c r="I6" s="7">
-        <f t="shared" si="0"/>
         <v>14208</v>
       </c>
       <c r="J6" s="7">
-        <f t="shared" si="1"/>
         <v>14208</v>
       </c>
       <c r="K6" s="7">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L6" s="7">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N6" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O6" s="8">
-        <f t="shared" ref="O6" si="15">Q6-(Q6*(P6/100))</f>
         <v>118.4</v>
       </c>
       <c r="P6" s="3">
@@ -2009,37 +1963,33 @@
       <c r="Q6" s="18">
         <v>296</v>
       </c>
-      <c r="R6" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>NO</v>
+      <c r="R6" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S6" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T6" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V6" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D7" s="3">
-        <f>F7-E7</f>
         <v>-1</v>
       </c>
       <c r="E7" s="3">
@@ -2049,33 +1999,26 @@
         <v>4</v>
       </c>
       <c r="G7" s="9"/>
-      <c r="H7" s="3"/>
+      <c r="H7" s="8"/>
       <c r="I7" s="7">
-        <f t="shared" si="0"/>
         <v>8640</v>
       </c>
       <c r="J7" s="7">
-        <f t="shared" si="1"/>
         <v>6912</v>
       </c>
       <c r="K7" s="7">
-        <f t="shared" si="2"/>
         <v>1728</v>
       </c>
       <c r="L7" s="7">
-        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M7" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N7" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O7" s="8">
-        <f>Q7-(Q7*(P7/100))</f>
         <v>72</v>
       </c>
       <c r="P7" s="3">
@@ -2084,23 +2027,20 @@
       <c r="Q7" s="18">
         <v>180</v>
       </c>
-      <c r="R7" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v>YES</v>
+      <c r="R7" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="S7" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T7" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U7" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V7" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2109,7 +2049,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="8"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -2124,16 +2064,15 @@
     </row>
     <row r="9" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D9" s="3">
-        <f t="shared" ref="D9" si="16">F9-E9</f>
         <v>0</v>
       </c>
       <c r="E9" s="3">
@@ -2143,33 +2082,28 @@
         <v>100</v>
       </c>
       <c r="G9" s="9"/>
-      <c r="H9" s="3"/>
+      <c r="H9" s="8">
+        <v>13368</v>
+      </c>
       <c r="I9" s="7">
-        <f t="shared" ref="I9" si="17">O9*E9*T9</f>
         <v>53999.999999999985</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" ref="J9" si="18">F9*O9*T9</f>
         <v>53999.999999999985</v>
       </c>
       <c r="K9" s="7">
-        <f t="shared" ref="K9" si="19">IF(D9&gt;0, 0, (-1)*D9*O9*T9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" ref="L9" si="20">IF(U9="FIXED", 0, IF(D9&lt;0, 0, D9*O9*T9))</f>
         <v>0</v>
       </c>
       <c r="M9" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N9" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O9" s="8">
-        <f t="shared" ref="O9" si="21">Q9-(Q9*(P9/100))</f>
         <v>22.499999999999996</v>
       </c>
       <c r="P9" s="6">
@@ -2178,37 +2112,33 @@
       <c r="Q9" s="18">
         <v>50</v>
       </c>
-      <c r="R9" s="9" t="str">
-        <f t="shared" ref="R9" si="22">IF(E9&gt;F9, "YES", "NO")</f>
-        <v>NO</v>
+      <c r="R9" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S9" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T9" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U9" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="V9" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3">
-        <f>F10-E10</f>
         <v>-50</v>
       </c>
       <c r="E10" s="3">
@@ -2218,33 +2148,26 @@
         <v>100</v>
       </c>
       <c r="G10" s="9"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="8"/>
       <c r="I10" s="7">
-        <f t="shared" ref="I10:I11" si="23">O10*E10*T10</f>
         <v>100440</v>
       </c>
       <c r="J10" s="7">
-        <f t="shared" ref="J10:J11" si="24">F10*O10*T10</f>
         <v>66960</v>
       </c>
       <c r="K10" s="7">
-        <f t="shared" ref="K10:K11" si="25">IF(D10&gt;0, 0, (-1)*D10*O10*T10)</f>
         <v>33480</v>
       </c>
       <c r="L10" s="7">
-        <f t="shared" ref="L10:L11" si="26">IF(U10="FIXED", 0, IF(D10&lt;0, 0, D10*O10*T10))</f>
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="N10" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O10" s="8">
-        <f>Q10-(Q10*(P10/100))</f>
         <v>27.9</v>
       </c>
       <c r="P10" s="6">
@@ -2253,37 +2176,33 @@
       <c r="Q10" s="18">
         <v>62</v>
       </c>
-      <c r="R10" s="9" t="str">
-        <f t="shared" ref="R10:R11" si="27">IF(E10&gt;F10, "YES", "NO")</f>
-        <v>YES</v>
+      <c r="R10" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="S10" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T10" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D11" s="3">
-        <f t="shared" ref="D11" si="28">F11-E11</f>
         <v>15</v>
       </c>
       <c r="E11" s="6">
@@ -2293,33 +2212,26 @@
         <v>65</v>
       </c>
       <c r="G11" s="9"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="7">
-        <f t="shared" si="23"/>
         <v>8639.9999999999982</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" si="24"/>
         <v>11231.999999999998</v>
       </c>
       <c r="K11" s="7">
-        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L11" s="7">
-        <f t="shared" si="26"/>
         <v>2591.9999999999995</v>
       </c>
       <c r="M11" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N11" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O11" s="8">
-        <f t="shared" ref="O11" si="29">Q11-(Q11*(P11/100))</f>
         <v>7.1999999999999993</v>
       </c>
       <c r="P11" s="6">
@@ -2328,37 +2240,33 @@
       <c r="Q11" s="18">
         <v>16</v>
       </c>
-      <c r="R11" s="9" t="str">
-        <f t="shared" si="27"/>
-        <v>NO</v>
+      <c r="R11" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S11" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T11" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" ref="D12" si="30">F12-E12</f>
         <v>10</v>
       </c>
       <c r="E12" s="6">
@@ -2368,29 +2276,23 @@
         <v>10</v>
       </c>
       <c r="G12" s="9"/>
-      <c r="H12" s="3"/>
+      <c r="H12" s="8"/>
       <c r="I12" s="7">
-        <f t="shared" ref="I12" si="31">O12*E12*T12</f>
         <v>0</v>
       </c>
       <c r="J12" s="7">
-        <f t="shared" ref="J12" si="32">F12*O12*T12</f>
         <v>17520</v>
       </c>
       <c r="K12" s="7">
-        <f t="shared" ref="K12" si="33">IF(D12&gt;0, 0, (-1)*D12*O12*T12)</f>
         <v>0</v>
       </c>
       <c r="L12" s="7">
-        <f t="shared" ref="L12" si="34">IF(U12="FIXED", 0, IF(D12&lt;0, 0, D12*O12*T12))</f>
         <v>17520</v>
       </c>
       <c r="M12" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N12" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O12" s="8">
@@ -2402,30 +2304,27 @@
       <c r="Q12" s="18">
         <v>618</v>
       </c>
-      <c r="R12" s="9" t="str">
-        <f t="shared" ref="R12" si="35">IF(E12&gt;F12, "YES", "NO")</f>
-        <v>NO</v>
+      <c r="R12" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S12" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T12" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="9"/>
       <c r="D13" s="3"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="3"/>
+      <c r="H13" s="8"/>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
@@ -2438,16 +2337,15 @@
     </row>
     <row r="14" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" s="3">
-        <f t="shared" ref="D14:D24" si="36">F14-E14</f>
         <v>0</v>
       </c>
       <c r="E14" s="3">
@@ -2457,33 +2355,28 @@
         <v>150</v>
       </c>
       <c r="G14" s="9"/>
-      <c r="H14" s="3"/>
+      <c r="H14" s="8">
+        <v>22276.80000000001</v>
+      </c>
       <c r="I14" s="7">
-        <f t="shared" ref="I14:I17" si="37">O14*E14*T14</f>
         <v>108000</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" ref="J14:J17" si="38">F14*O14*T14</f>
         <v>108000</v>
       </c>
       <c r="K14" s="7">
-        <f t="shared" ref="K14:K17" si="39">IF(D14&gt;0, 0, (-1)*D14*O14*T14)</f>
         <v>0</v>
       </c>
       <c r="L14" s="7">
-        <f t="shared" ref="L14:L17" si="40">IF(U14="FIXED", 0, IF(D14&lt;0, 0, D14*O14*T14))</f>
         <v>0</v>
       </c>
       <c r="M14" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N14" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O14" s="8">
-        <f t="shared" ref="O14:O24" si="41">Q14-(Q14*(P14/100))</f>
         <v>30</v>
       </c>
       <c r="P14" s="6">
@@ -2492,37 +2385,33 @@
       <c r="Q14" s="18">
         <v>100</v>
       </c>
-      <c r="R14" s="9" t="str">
-        <f t="shared" ref="R14:R17" si="42">IF(E14&gt;F14, "YES", "NO")</f>
-        <v>NO</v>
+      <c r="R14" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S14" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T14" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U14" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="C15" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" s="3">
-        <f t="shared" si="36"/>
         <v>-5</v>
       </c>
       <c r="E15" s="3">
@@ -2532,33 +2421,26 @@
         <v>10</v>
       </c>
       <c r="G15" s="9"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="8"/>
       <c r="I15" s="7">
-        <f>O15*E15*T15</f>
         <v>88884.000000000029</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="38"/>
         <v>59256.000000000022</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="39"/>
         <v>29628.000000000011</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N15" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O15" s="8">
-        <f t="shared" si="41"/>
         <v>246.90000000000009</v>
       </c>
       <c r="P15" s="6">
@@ -2567,37 +2449,33 @@
       <c r="Q15" s="18">
         <v>823</v>
       </c>
-      <c r="R15" s="9" t="str">
-        <f t="shared" si="42"/>
-        <v>YES</v>
+      <c r="R15" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="S15" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T15" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" si="36"/>
         <v>-1</v>
       </c>
       <c r="E16" s="3">
@@ -2607,33 +2485,26 @@
         <v>1</v>
       </c>
       <c r="G16" s="9"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="8"/>
       <c r="I16" s="7">
-        <f t="shared" si="37"/>
         <v>6609.6000000000022</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" si="38"/>
         <v>3304.8000000000011</v>
       </c>
       <c r="K16" s="7">
-        <f t="shared" si="39"/>
         <v>3304.8000000000011</v>
       </c>
       <c r="L16" s="7">
-        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="M16" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N16" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" si="41"/>
         <v>137.70000000000005</v>
       </c>
       <c r="P16" s="6">
@@ -2642,37 +2513,33 @@
       <c r="Q16" s="18">
         <v>459</v>
       </c>
-      <c r="R16" s="9" t="str">
-        <f t="shared" si="42"/>
-        <v>YES</v>
+      <c r="R16" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="S16" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T16" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U16" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" si="36"/>
         <v>2</v>
       </c>
       <c r="E17" s="6">
@@ -2682,33 +2549,26 @@
         <v>2</v>
       </c>
       <c r="G17" s="9"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="8"/>
       <c r="I17" s="7">
-        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" si="38"/>
         <v>10656</v>
       </c>
       <c r="K17" s="7">
-        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="L17" s="7">
-        <f t="shared" si="40"/>
         <v>10656</v>
       </c>
       <c r="M17" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N17" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O17" s="8">
-        <f t="shared" si="41"/>
         <v>222</v>
       </c>
       <c r="P17" s="6">
@@ -2717,29 +2577,26 @@
       <c r="Q17" s="18">
         <v>740</v>
       </c>
-      <c r="R17" s="9" t="str">
-        <f t="shared" si="42"/>
-        <v>NO</v>
+      <c r="R17" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S17" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T17" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U17" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V17" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D18" s="3"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="8"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
@@ -2752,16 +2609,15 @@
     </row>
     <row r="19" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="E19" s="3">
@@ -2770,33 +2626,28 @@
       <c r="F19" s="3">
         <v>30</v>
       </c>
-      <c r="H19" s="3"/>
+      <c r="H19" s="8">
+        <v>188364</v>
+      </c>
       <c r="I19" s="7">
-        <f t="shared" ref="I19:I24" si="43">O19*E19*T19</f>
         <v>133560</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" ref="J19:J24" si="44">F19*O19*T19</f>
         <v>133560</v>
       </c>
       <c r="K19" s="7">
-        <f t="shared" ref="K19:K24" si="45">IF(D19&gt;0, 0, (-1)*D19*O19*T19)</f>
         <v>0</v>
       </c>
       <c r="L19" s="7">
-        <f t="shared" ref="L19:L24" si="46">IF(U19="FIXED", 0, IF(D19&lt;0, 0, D19*O19*T19))</f>
         <v>0</v>
       </c>
       <c r="M19" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N19" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" si="41"/>
         <v>185.5</v>
       </c>
       <c r="P19" s="6">
@@ -2805,37 +2656,33 @@
       <c r="Q19" s="18">
         <v>371</v>
       </c>
-      <c r="R19" s="9" t="str">
-        <f t="shared" ref="R19:R24" si="47">IF(E19&gt;F19, "YES", "NO")</f>
-        <v>NO</v>
+      <c r="R19" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S19" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T19" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="C20" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D20" s="3">
-        <f t="shared" si="36"/>
         <v>100</v>
       </c>
       <c r="E20" s="3">
@@ -2844,33 +2691,26 @@
       <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3"/>
+      <c r="H20" s="8"/>
       <c r="I20" s="7">
-        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J20" s="7">
-        <f t="shared" si="44"/>
         <v>92400</v>
       </c>
       <c r="K20" s="7">
-        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L20" s="7">
-        <f t="shared" si="46"/>
         <v>92400</v>
       </c>
       <c r="M20" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O20" s="8">
-        <f t="shared" si="41"/>
         <v>38.5</v>
       </c>
       <c r="P20" s="6">
@@ -2879,37 +2719,33 @@
       <c r="Q20" s="18">
         <v>77</v>
       </c>
-      <c r="R20" s="9" t="str">
-        <f t="shared" si="47"/>
-        <v>NO</v>
+      <c r="R20" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S20" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T20" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U20" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V20" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D21" s="3">
-        <f t="shared" si="36"/>
         <v>-75</v>
       </c>
       <c r="E21" s="3">
@@ -2918,33 +2754,26 @@
       <c r="F21" s="3">
         <v>25</v>
       </c>
-      <c r="H21" s="3"/>
+      <c r="H21" s="8"/>
       <c r="I21" s="7">
-        <f t="shared" si="43"/>
         <v>368400</v>
       </c>
       <c r="J21" s="7">
-        <f t="shared" si="44"/>
         <v>92100</v>
       </c>
       <c r="K21" s="7">
-        <f t="shared" si="45"/>
         <v>276300</v>
       </c>
       <c r="L21" s="7">
-        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M21" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N21" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O21" s="8">
-        <f t="shared" si="41"/>
         <v>153.5</v>
       </c>
       <c r="P21" s="6">
@@ -2953,37 +2782,33 @@
       <c r="Q21" s="18">
         <v>307</v>
       </c>
-      <c r="R21" s="9" t="str">
-        <f t="shared" si="47"/>
-        <v>YES</v>
+      <c r="R21" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="S21" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T21" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U21" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V21" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D22" s="3">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="E22" s="3">
@@ -2992,33 +2817,26 @@
       <c r="F22" s="3">
         <v>2</v>
       </c>
-      <c r="H22" s="3"/>
+      <c r="H22" s="8"/>
       <c r="I22" s="7">
-        <f t="shared" si="43"/>
         <v>3072</v>
       </c>
       <c r="J22" s="7">
-        <f t="shared" si="44"/>
         <v>3072</v>
       </c>
       <c r="K22" s="7">
-        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L22" s="7">
-        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M22" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O22" s="8">
-        <f t="shared" si="41"/>
         <v>64</v>
       </c>
       <c r="P22" s="6">
@@ -3027,37 +2845,33 @@
       <c r="Q22" s="18">
         <v>128</v>
       </c>
-      <c r="R22" s="9" t="str">
-        <f t="shared" si="47"/>
-        <v>NO</v>
+      <c r="R22" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S22" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T22" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U22" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V22" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D23" s="3">
-        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="E23" s="3">
@@ -3066,33 +2880,26 @@
       <c r="F23" s="3">
         <v>1</v>
       </c>
-      <c r="H23" s="3"/>
+      <c r="H23" s="8"/>
       <c r="I23" s="7">
-        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J23" s="7">
-        <f t="shared" si="44"/>
         <v>5736</v>
       </c>
       <c r="K23" s="7">
-        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L23" s="7">
-        <f t="shared" si="46"/>
         <v>5736</v>
       </c>
       <c r="M23" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N23" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O23" s="8">
-        <f t="shared" si="41"/>
         <v>239</v>
       </c>
       <c r="P23" s="6">
@@ -3101,37 +2908,33 @@
       <c r="Q23" s="18">
         <v>478</v>
       </c>
-      <c r="R23" s="9" t="str">
-        <f t="shared" si="47"/>
-        <v>NO</v>
+      <c r="R23" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="S23" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T23" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V23" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:22" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="36"/>
         <v>-10</v>
       </c>
       <c r="E24" s="6">
@@ -3140,33 +2943,26 @@
       <c r="F24" s="6">
         <v>0</v>
       </c>
-      <c r="H24" s="3"/>
+      <c r="H24" s="8"/>
       <c r="I24" s="7">
-        <f t="shared" si="43"/>
         <v>10200</v>
       </c>
       <c r="J24" s="7">
-        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="K24" s="7">
-        <f t="shared" si="45"/>
         <v>10200</v>
       </c>
       <c r="L24" s="7">
-        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N24" s="3">
-        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O24" s="8">
-        <f t="shared" si="41"/>
         <v>42.5</v>
       </c>
       <c r="P24" s="6">
@@ -3175,28 +2971,23 @@
       <c r="Q24" s="18">
         <v>85</v>
       </c>
-      <c r="R24" s="9" t="str">
-        <f t="shared" si="47"/>
-        <v>YES</v>
+      <c r="R24" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="S24" s="6">
-        <f>Summary!$B$9</f>
         <v>36</v>
       </c>
       <c r="T24" s="6">
-        <f>Summary!$B$10</f>
         <v>24</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="V24" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>